--- a/racecards/racecard_20260708.xlsx
+++ b/racecards/racecard_20260708.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO123"/>
+  <dimension ref="A1:AO122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,7 +667,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -692,7 +696,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -745,10 +749,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1170</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -838,7 +844,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -863,7 +873,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -916,10 +926,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1009,7 +1021,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -1087,10 +1103,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1193</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1180,7 +1198,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -1191,7 +1213,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CONSPIRATOR</t>
+          <t>CONSPIRATOR (Scratched)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1204,29 +1226,27 @@
           <t>K090</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>5</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>L Hewitson</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B Crawford</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>132</v>
-      </c>
-      <c r="T5" t="n">
-        <v>36</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1234,24 +1254,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="W5" t="n">
-        <v>5</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9/10/12/13/8/5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>+ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1262,7 +1284,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.57.67</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1272,30 +1294,28 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>175,500</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>49</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Ng Sun Wah, Au Yau Lin &amp; Alan Leung Wai Zen</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Daiwa Major</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Get Closer</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AM5" t="b">
@@ -1347,7 +1367,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -1372,7 +1396,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1425,10 +1449,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1186</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1514,7 +1540,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -1539,7 +1569,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1592,10 +1622,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -1681,7 +1713,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -1759,10 +1795,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1114</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -1848,7 +1886,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -1926,10 +1968,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1070</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -2019,7 +2063,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -2044,7 +2092,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -2097,10 +2145,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -2186,7 +2236,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -2211,7 +2265,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -2264,10 +2318,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -2357,7 +2413,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -2382,7 +2442,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -2435,10 +2495,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1260</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -2528,7 +2590,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -2606,10 +2672,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2699,7 +2767,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -2751,7 +2823,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -2810,7 +2884,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -2862,7 +2940,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -2921,7 +3001,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -2999,10 +3083,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>1139</v>
+      </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -3092,7 +3178,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3166,10 +3256,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1207</v>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3259,7 +3351,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3333,10 +3429,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>1064</v>
+      </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
@@ -3422,7 +3520,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3496,10 +3598,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>974</v>
+      </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -3589,7 +3693,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3667,10 +3775,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>1071</v>
+      </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3760,7 +3870,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -3838,10 +3952,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>1167</v>
+      </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3931,7 +4047,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4005,10 +4125,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>1094</v>
+      </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -4094,7 +4216,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4172,10 +4298,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>1120</v>
+      </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -4261,7 +4389,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4339,10 +4471,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>1096</v>
+      </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -4432,7 +4566,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4510,10 +4648,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>1103</v>
+      </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -4603,7 +4743,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4681,10 +4825,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -4774,7 +4920,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -4856,10 +5006,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>1027</v>
+      </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -4949,7 +5101,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5001,7 +5157,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>1086</v>
+      </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
@@ -5060,7 +5218,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5112,7 +5274,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>1150</v>
+      </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
@@ -5171,7 +5335,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5249,10 +5417,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -5342,7 +5512,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5420,10 +5594,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>990</v>
+      </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -5513,7 +5689,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5591,10 +5771,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>1145</v>
+      </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -5684,7 +5866,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5762,10 +5948,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>1194</v>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5855,7 +6043,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -5933,10 +6125,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>1079</v>
+      </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -6026,7 +6220,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6104,10 +6302,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>1021</v>
+      </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
@@ -6193,7 +6393,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6267,10 +6471,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>1035</v>
+      </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -6360,7 +6566,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6438,10 +6648,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>1116</v>
+      </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
@@ -6531,7 +6743,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6609,10 +6825,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>1046</v>
+      </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+40</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -6702,7 +6920,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6780,10 +7002,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>1073</v>
+      </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -6873,7 +7097,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -6951,10 +7179,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>1187</v>
+      </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -7044,7 +7274,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7122,10 +7356,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>1202</v>
+      </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -7215,7 +7451,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7267,7 +7507,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>1053</v>
+      </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
@@ -7326,7 +7568,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7378,7 +7624,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>1195</v>
+      </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
@@ -7437,7 +7685,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7515,10 +7767,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>1107</v>
+      </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -7608,7 +7862,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7686,10 +7944,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>1138</v>
+      </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -7779,7 +8039,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -7857,10 +8121,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>1051</v>
+      </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
@@ -7950,7 +8216,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8028,10 +8298,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>1133</v>
+      </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
@@ -8121,7 +8393,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8195,10 +8471,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>1073</v>
+      </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -8284,7 +8562,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8358,10 +8640,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>1069</v>
+      </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -8451,7 +8735,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8529,10 +8817,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>1060</v>
+      </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -8622,7 +8912,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8700,10 +8994,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
@@ -8793,7 +9089,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8845,7 +9145,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>1010</v>
+      </c>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
@@ -8904,7 +9206,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -8956,7 +9262,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>1051</v>
+      </c>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
@@ -9015,7 +9323,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9093,10 +9405,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>1180</v>
+      </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
@@ -9182,7 +9496,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9260,10 +9578,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>1143</v>
+      </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
@@ -9353,7 +9673,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9431,10 +9755,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>1022</v>
+      </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
@@ -9524,7 +9850,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9602,10 +9932,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>1113</v>
+      </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -9695,7 +10027,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9773,7 +10109,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>1087</v>
+      </c>
       <c r="AD58" t="inlineStr">
         <is>
           <t>-</t>
@@ -9860,7 +10198,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -9938,10 +10280,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -10031,7 +10375,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10109,10 +10457,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>1099</v>
+      </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
@@ -10202,7 +10552,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10280,10 +10634,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>1049</v>
+      </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -10369,7 +10725,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10447,10 +10807,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>1048</v>
+      </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
@@ -10540,7 +10902,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10618,10 +10984,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
@@ -10711,7 +11079,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10785,10 +11157,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>1076</v>
+      </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
@@ -10878,7 +11252,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -10956,10 +11334,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -11049,7 +11429,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -11101,7 +11485,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>1052</v>
+      </c>
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr"/>
@@ -11160,7 +11546,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -11212,7 +11602,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>1147</v>
+      </c>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
@@ -11271,7 +11663,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -11349,10 +11745,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>1286</v>
+      </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
@@ -11442,7 +11840,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -11520,10 +11922,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>1133</v>
+      </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -11613,7 +12017,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -11691,10 +12099,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>1046</v>
+      </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
@@ -11784,7 +12194,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -11862,10 +12276,12 @@
           <t>+ 2</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>1033</v>
+      </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
@@ -11955,7 +12371,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -12033,10 +12453,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>1046</v>
+      </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
@@ -12126,7 +12548,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -12204,10 +12630,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>1056</v>
+      </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -12297,7 +12725,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -12375,10 +12807,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>1122</v>
+      </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -12468,7 +12902,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -12546,10 +12984,12 @@
           <t>+ 2</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
@@ -12639,7 +13079,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -12713,10 +13157,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
@@ -12806,7 +13252,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -12884,10 +13334,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>1015</v>
+      </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
@@ -12977,7 +13429,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13055,10 +13511,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
@@ -13148,7 +13606,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13226,10 +13688,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>1137</v>
+      </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
@@ -13319,7 +13783,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13371,7 +13839,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
@@ -13430,7 +13900,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -13482,7 +13956,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>996</v>
+      </c>
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr"/>
@@ -13623,10 +14099,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>1139</v>
+      </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -13798,10 +14276,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>1031</v>
+      </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
@@ -13973,10 +14453,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>1302</v>
+      </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE84" t="inlineStr">
@@ -14148,10 +14630,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-35</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -14323,10 +14807,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>1047</v>
+      </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr"/>
@@ -14494,7 +14980,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>1081</v>
+      </c>
       <c r="AD87" t="inlineStr">
         <is>
           <t>-</t>
@@ -14663,10 +15151,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>1216</v>
+      </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
@@ -14838,10 +15328,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>1078</v>
+      </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr"/>
@@ -15009,10 +15501,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>1058</v>
+      </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -15184,10 +15678,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr"/>
+      <c r="AC91" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
@@ -15355,10 +15851,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr"/>
+      <c r="AC92" t="n">
+        <v>1130</v>
+      </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE92" t="inlineStr">
@@ -15534,10 +16032,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr"/>
+      <c r="AC93" t="n">
+        <v>1137</v>
+      </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -15683,7 +16183,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr"/>
+      <c r="AC94" t="n">
+        <v>1220</v>
+      </c>
       <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
@@ -15798,7 +16300,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr"/>
+      <c r="AC95" t="n">
+        <v>1070</v>
+      </c>
       <c r="AD95" t="inlineStr"/>
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
@@ -15857,7 +16361,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -15935,10 +16443,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr"/>
+      <c r="AC96" t="n">
+        <v>1211</v>
+      </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -16028,7 +16538,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -16102,10 +16616,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr"/>
+      <c r="AC97" t="n">
+        <v>1232</v>
+      </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
@@ -16195,7 +16711,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -16273,10 +16793,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr"/>
+      <c r="AC98" t="n">
+        <v>1143</v>
+      </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -16366,7 +16888,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -16444,10 +16970,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>1081</v>
+      </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr"/>
@@ -16533,7 +17061,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -16611,10 +17143,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>1030</v>
+      </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
@@ -16704,7 +17238,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -16715,17 +17253,17 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>WITHOUT COMPARE</t>
+          <t>ROMANTIC THOR</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>HK_2025_L151</t>
+          <t>HK_2024_K012</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>L151</t>
+          <t>K012</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -16743,14 +17281,14 @@
         </is>
       </c>
       <c r="S101" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="T101" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -16759,7 +17297,7 @@
         </is>
       </c>
       <c r="W101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -16769,26 +17307,32 @@
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>1/2/1/4/2/4</t>
+          <t>3/4/1/4/2/3</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>XB/TT</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC101" t="n">
+        <v>1071</v>
+      </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr"/>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>1.48.49</t>
+        </is>
+      </c>
       <c r="AF101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16796,25 +17340,25 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>5,242,300</t>
+          <t>6,027,250</t>
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Elaine Wong</t>
+          <t>Peter Lau Pak Fai &amp; Suki Tang Xianfang</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>Brutal</t>
+          <t>Justify</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Command More</t>
+          <t>Wedding Vow</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
@@ -16871,7 +17415,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -16945,10 +17493,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
@@ -17038,7 +17588,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -17116,10 +17670,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr"/>
+      <c r="AC103" t="n">
+        <v>1140</v>
+      </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
@@ -17209,7 +17765,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -17287,10 +17847,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr"/>
+      <c r="AC104" t="n">
+        <v>1039</v>
+      </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
@@ -17380,7 +17942,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -17458,10 +18024,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>1018</v>
+      </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
@@ -17551,7 +18119,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -17629,10 +18201,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr"/>
+      <c r="AC106" t="n">
+        <v>1151</v>
+      </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr"/>
@@ -17718,7 +18292,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -17796,10 +18374,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
@@ -17889,18 +18469,22 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>90-65</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>ROMANTIC THOR</t>
+          <t>SKY VINO</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -17910,30 +18494,30 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>C Fownes</t>
         </is>
       </c>
       <c r="S108" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="T108" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>3/4/1/4/2/3</t>
+          <t>4/6/1/2/6/7</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>XB/TT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
@@ -17941,7 +18525,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD108" t="inlineStr"/>
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr"/>
@@ -17977,18 +18563,18 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>HAT TRICK HANDICAP</t>
+          <t>PENALTY SHOOTOUT HANDICAP</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -18000,79 +18586,145 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>90-65</t>
+          <t>80-60</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>SKY VINO</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
+          <t>AURIO</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>HK_2024_K056</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>K056</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>3</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>H Bowman</t>
+        </is>
+      </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>C Fownes</t>
+          <t>K L Man</t>
         </is>
       </c>
       <c r="S109" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="T109" t="n">
-        <v>80</v>
-      </c>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="W109" t="n">
-        <v>4</v>
-      </c>
-      <c r="X109" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>4/6/1/2/6/7</t>
+          <t>5/3/2/1/4/4</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>SR/TT</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr"/>
-      <c r="AD109" t="inlineStr"/>
-      <c r="AE109" t="inlineStr"/>
-      <c r="AF109" t="inlineStr"/>
-      <c r="AG109" t="inlineStr"/>
-      <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr"/>
-      <c r="AJ109" t="inlineStr"/>
-      <c r="AK109" t="inlineStr"/>
-      <c r="AL109" t="inlineStr"/>
+          <t>+ 1</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>1160</v>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>1.08.49</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>3,225,900</t>
+        </is>
+      </c>
+      <c r="AH109" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Lucky Six Syndicate</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>Capitalist</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Madame Cactus</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="AM109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>HK$3,120,000,</t>
+          <t>HK$1,860,000,</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:50</t>
         </is>
       </c>
     </row>
@@ -18111,49 +18763,53 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>AURIO</t>
+          <t>JUBILANT WINNER</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>HK_2024_K056</t>
+          <t>HK_2023_J346</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>K056</t>
+          <t>J346</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>H Bowman</t>
+          <t>A Atzeni</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>K L Man</t>
+          <t>J Richards</t>
         </is>
       </c>
       <c r="S110" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="T110" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -18176,28 +18832,30 @@
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>5/3/2/1/4/4</t>
+          <t>5/10/1/4/1/4</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>SR/TT</t>
+          <t>B/TT</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>+ 1</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr"/>
+          <t>* 1</t>
+        </is>
+      </c>
+      <c r="AC110" t="n">
+        <v>1208</v>
+      </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>1.08.49</t>
+          <t>1.09.33</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -18207,15 +18865,15 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>3,225,900</t>
+          <t>3,681,900</t>
         </is>
       </c>
       <c r="AH110" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Lucky Six Syndicate</t>
+          <t>Happy Valley Brothers Syndicate</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -18225,12 +18883,12 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Madame Cactus</t>
+          <t>We Can Dance</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="AM110" t="b">
@@ -18282,49 +18940,53 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>JUBILANT WINNER</t>
+          <t>DO YOU JUST</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>HK_2023_J346</t>
+          <t>HK_2025_L094</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>J346</t>
+          <t>L094</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>A Atzeni</t>
+          <t>Y L Chung (-2)</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>J Richards</t>
+          <t>A S Cruz</t>
         </is>
       </c>
       <c r="S111" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="T111" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -18337,7 +18999,7 @@
         </is>
       </c>
       <c r="W111" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -18347,28 +19009,30 @@
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>5/10/1/4/1/4</t>
+          <t>9/7/1/6/5/11</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>B/TT</t>
+          <t>CP/TT</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>* 1</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr"/>
+          <t>+ 1</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>1.09.33</t>
+          <t>1.09.45</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -18378,30 +19042,30 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>3,681,900</t>
+          <t>2,643,900</t>
         </is>
       </c>
       <c r="AH111" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Happy Valley Brothers Syndicate</t>
+          <t>Speed Legend Syndicate</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>Capitalist</t>
+          <t>So You Think</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>We Can Dance</t>
+          <t>Estijmaam</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AM111" t="b">
@@ -18453,53 +19117,57 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>DO YOU JUST</t>
+          <t>TARGET AUDIENCE</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>HK_2025_L094</t>
+          <t>HK_2024_K107</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>L094</t>
+          <t>K107</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Y L Chung (-2)</t>
+          <t>J Moreira</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>A S Cruz</t>
+          <t>C Fownes</t>
         </is>
       </c>
       <c r="S112" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T112" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -18508,7 +19176,7 @@
         </is>
       </c>
       <c r="W112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
@@ -18518,28 +19186,30 @@
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>9/7/1/6/5/11</t>
+          <t>1/5/5/1/5/8</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>CP/TT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>+ 1</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>1.09.45</t>
+          <t>1.09.38</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -18549,25 +19219,25 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>2,643,900</t>
+          <t>3,327,000</t>
         </is>
       </c>
       <c r="AH112" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Speed Legend Syndicate</t>
+          <t>Wong Yuen Man</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>So You Think</t>
+          <t>Derryn</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Estijmaam</t>
+          <t>Magic Tryst</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
@@ -18624,53 +19294,57 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>TARGET AUDIENCE</t>
+          <t>NORTHERN FIRE BALL</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>HK_2024_K107</t>
+          <t>HK_2023_J488</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>K107</t>
+          <t>J488</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>J Moreira</t>
+          <t>K C Leung</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>C Fownes</t>
+          <t>C H Yip</t>
         </is>
       </c>
       <c r="S113" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="T113" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -18689,7 +19363,7 @@
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>1/5/5/1/5/8</t>
+          <t>6/1/12/4/1/4</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -18699,18 +19373,20 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr"/>
+          <t>* 1</t>
+        </is>
+      </c>
+      <c r="AC113" t="n">
+        <v>1155</v>
+      </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>1.09.38</t>
+          <t>1.09.55</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -18720,7 +19396,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>3,327,000</t>
+          <t>1,511,400</t>
         </is>
       </c>
       <c r="AH113" t="n">
@@ -18728,22 +19404,22 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Wong Yuen Man</t>
+          <t>Ricky Chiu Tong</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>Derryn</t>
+          <t>Sooboog</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Magic Tryst</t>
+          <t>Andronica</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="AM113" t="b">
@@ -18795,42 +19471,46 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>NORTHERN FIRE BALL</t>
+          <t>POWER KOEPP</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>HK_2023_J488</t>
+          <t>HK_2020_E301</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>J488</t>
+          <t>E301</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>K C Leung</t>
+          <t>A Badel</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>C H Yip</t>
+          <t>M Newnham</t>
         </is>
       </c>
       <c r="S114" t="n">
@@ -18841,7 +19521,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -18850,7 +19530,7 @@
         </is>
       </c>
       <c r="W114" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -18860,28 +19540,30 @@
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>6/1/12/4/1/4</t>
+          <t>1/6/6/4/3/11</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>* 1</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC114" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>1.09.55</t>
+          <t>1.09.02</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -18891,30 +19573,30 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>1,511,400</t>
+          <t>1,804,200</t>
         </is>
       </c>
       <c r="AH114" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Ricky Chiu Tong</t>
+          <t>Mr &amp; Mrs Simon Ng Kar Ming</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>Sooboog</t>
+          <t>Equiano</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Andronica</t>
+          <t>Terse</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AM114" t="b">
@@ -18966,53 +19648,57 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K115" t="n">
+        <v>7</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>KING PROFIT</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>HK_2023_J539</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>J539</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
         <v>6</v>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>POWER KOEPP</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>HK_2020_E301</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>E301</t>
-        </is>
-      </c>
-      <c r="O115" t="n">
-        <v>7</v>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>A Badel</t>
+          <t>Z Purton</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>M Newnham</t>
+          <t>C S Shum</t>
         </is>
       </c>
       <c r="S115" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T115" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -19021,7 +19707,7 @@
         </is>
       </c>
       <c r="W115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
@@ -19031,12 +19717,12 @@
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>1/6/6/4/3/11</t>
+          <t>2/1/2/2/5/4</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
@@ -19044,15 +19730,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr"/>
+      <c r="AC115" t="n">
+        <v>1081</v>
+      </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>1.09.02</t>
+          <t>1.09.25</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -19062,7 +19750,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>1,804,200</t>
+          <t>1,648,350</t>
         </is>
       </c>
       <c r="AH115" t="n">
@@ -19070,17 +19758,17 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Mr &amp; Mrs Simon Ng Kar Ming</t>
+          <t>Mr &amp; Mrs William Yem Wai Lai, Stanley Yem Chee Hong and Sammy Yem Chee Long</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>Equiano</t>
+          <t>Stratosphere</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Terse</t>
+          <t>Digger's Girl</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
@@ -19137,53 +19825,57 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>KING PROFIT</t>
+          <t>HONEST WITNESS</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>HK_2023_J539</t>
+          <t>HK_2024_K283</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>J539</t>
+          <t>K283</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>P N Wong (-7)</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>D A Hayes</t>
         </is>
       </c>
       <c r="S116" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="T116" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -19192,7 +19884,7 @@
         </is>
       </c>
       <c r="W116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
@@ -19202,12 +19894,12 @@
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>2/1/2/2/5/4</t>
+          <t>2/12/1/1/8/11</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>B/TT</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
@@ -19215,15 +19907,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr"/>
+      <c r="AC116" t="n">
+        <v>1087</v>
+      </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>1.09.25</t>
+          <t>1.09.45</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -19233,30 +19927,30 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>1,648,350</t>
+          <t>1,987,650</t>
         </is>
       </c>
       <c r="AH116" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Mr &amp; Mrs William Yem Wai Lai, Stanley Yem Chee Hong and Sammy Yem Chee Long</t>
+          <t>Arthur Antonio da Silva, Betty da Silva &amp; Teresa Marie da Silva</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>Stratosphere</t>
+          <t>Written By</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Digger's Girl</t>
+          <t>Sudden Wealth</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="AM116" t="b">
@@ -19308,42 +20002,46 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>HONEST WITNESS</t>
+          <t>MASTER CHAMPION</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>HK_2024_K283</t>
+          <t>HK_2024_K266</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>K283</t>
+          <t>K266</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>P N Wong (-7)</t>
+          <t>C Y Ho</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>P C Ng</t>
         </is>
       </c>
       <c r="S117" t="n">
@@ -19354,7 +20052,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -19373,28 +20071,30 @@
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>2/12/1/1/8/11</t>
+          <t>12/4/12/12/1/2</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>B/TT</t>
+          <t>CP-/TT-</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr"/>
+          <t>* 1</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>1215</v>
+      </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>1.09.45</t>
+          <t>1.09.80</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -19404,30 +20104,30 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>1,987,650</t>
+          <t>1,012,500</t>
         </is>
       </c>
       <c r="AH117" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Arthur Antonio da Silva, Betty da Silva &amp; Teresa Marie da Silva</t>
+          <t>Gainesville Syndicate</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>Written By</t>
+          <t>I Am Invincible</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Sudden Wealth</t>
+          <t>Dendee</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="AM117" t="b">
@@ -19479,53 +20179,61 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>MASTER CHAMPION</t>
+          <t>FRIENDS OF SHAJING</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>HK_2024_K266</t>
+          <t>HK_2024_K202</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>K266</t>
+          <t>K202</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>C Y Ho</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr"/>
+          <t>C L Chau (-2)</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>P C Ng</t>
+          <t>W K Mo</t>
         </is>
       </c>
       <c r="S118" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T118" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -19544,28 +20252,30 @@
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12/4/12/12/1/2</t>
+          <t>4/7/4/4/2/8</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>CP-/TT-</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>* 1</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr"/>
+          <t>+ 1</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>1.09.80</t>
+          <t>1.09.46</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -19575,25 +20285,25 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>1,012,500</t>
+          <t>725,400</t>
         </is>
       </c>
       <c r="AH118" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Gainesville Syndicate</t>
+          <t>Friends of Shajing Syndicate</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>I Am Invincible</t>
+          <t>Sergei Prokofiev</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Dendee</t>
+          <t>True Potential</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
@@ -19650,46 +20360,46 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>FRIENDS OF SHAJING</t>
+          <t>WINGS OF WAR</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>HK_2024_K202</t>
+          <t>HK_2022_H162</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>K202</t>
+          <t>H162</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>C L Chau (-2)</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>K Teetan</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>W K Mo</t>
+          <t>D J Whyte</t>
         </is>
       </c>
       <c r="S119" t="n">
@@ -19700,7 +20410,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -19709,7 +20419,7 @@
         </is>
       </c>
       <c r="W119" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
@@ -19719,28 +20429,30 @@
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>4/7/4/4/2/8</t>
+          <t>5/7/5/6/7/6</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>+ 1</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr"/>
+          <t>* 1</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>1183</v>
+      </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>1.09.46</t>
+          <t>1.09.28</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -19750,25 +20462,25 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>725,400</t>
+          <t>241,800</t>
         </is>
       </c>
       <c r="AH119" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Friends of Shajing Syndicate</t>
+          <t>Mary Slack</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>Sergei Prokofiev</t>
+          <t>Dark Angel</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>True Potential</t>
+          <t>Futoon</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
@@ -19825,53 +20537,57 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>WINGS OF WAR</t>
+          <t>CENTRAL BANK</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>HK_2022_H162</t>
+          <t>HK_2025_L222</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>H162</t>
+          <t>L222</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>K Teetan</t>
+          <t>L Hewitson</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>D J Whyte</t>
+          <t>D Eustace</t>
         </is>
       </c>
       <c r="S120" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T120" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -19880,7 +20596,7 @@
         </is>
       </c>
       <c r="W120" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
@@ -19890,30 +20606,28 @@
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>5/7/5/6/7/6</t>
+          <t>7/5/10/11</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>XB-</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>* 1</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr"/>
+          <t>+ 1</t>
+        </is>
+      </c>
+      <c r="AC120" t="n">
+        <v>965</v>
+      </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>1.09.28</t>
-        </is>
-      </c>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr">
         <is>
           <t>-</t>
@@ -19921,25 +20635,25 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>241,800</t>
+          <t>65,100</t>
         </is>
       </c>
       <c r="AH120" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Mary Slack</t>
+          <t>Ewo Syndicate</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>Dark Angel</t>
+          <t>Ten Sovereigns</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Futoon</t>
+          <t>Petit Leon</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
@@ -19996,126 +20710,76 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K121" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CENTRAL BANK</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>HK_2025_L222</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>L222</t>
-        </is>
-      </c>
-      <c r="O121" t="n">
-        <v>12</v>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>L Hewitson</t>
-        </is>
-      </c>
+          <t>THUNDER KIT</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>D Eustace</t>
+          <t>K W Lui</t>
         </is>
       </c>
       <c r="S121" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="T121" t="n">
-        <v>62</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="n">
         <v>4</v>
       </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
+      <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>7/5/10/11</t>
+          <t>3/11/1/2/4/3</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>XB-</t>
+          <t>H</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>+ 1</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr"/>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>1185</v>
+      </c>
+      <c r="AD121" t="inlineStr"/>
       <c r="AE121" t="inlineStr"/>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>65,100</t>
-        </is>
-      </c>
-      <c r="AH121" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>Ewo Syndicate</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>Ten Sovereigns</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Petit Leon</t>
-        </is>
-      </c>
-      <c r="AL121" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="inlineStr"/>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
       <c r="AM121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
@@ -20163,18 +20827,22 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>80-60</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>THUNDER KIT</t>
+          <t>CLASS</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -20184,14 +20852,14 @@
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>P F Yiu</t>
         </is>
       </c>
       <c r="S122" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="T122" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
@@ -20202,12 +20870,12 @@
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>3/11/1/2/4/3</t>
+          <t>9/12/13/13/12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>V/TT</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
@@ -20215,7 +20883,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr"/>
+      <c r="AC122" t="n">
+        <v>1157</v>
+      </c>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
@@ -20234,117 +20904,6 @@
         </is>
       </c>
       <c r="AO122" t="inlineStr">
-        <is>
-          <t>22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>HV</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>9</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>PENALTY SHOOTOUT HANDICAP</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>3</v>
-      </c>
-      <c r="F123" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>80-60</t>
-        </is>
-      </c>
-      <c r="K123" t="n">
-        <v>2</v>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>CLASS</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>P F Yiu</t>
-        </is>
-      </c>
-      <c r="S123" t="n">
-        <v>118</v>
-      </c>
-      <c r="T123" t="n">
-        <v>61</v>
-      </c>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="n">
-        <v>4</v>
-      </c>
-      <c r="X123" t="inlineStr"/>
-      <c r="Y123" t="inlineStr"/>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>9/12/13/13/12</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>V/TT</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr"/>
-      <c r="AD123" t="inlineStr"/>
-      <c r="AE123" t="inlineStr"/>
-      <c r="AF123" t="inlineStr"/>
-      <c r="AG123" t="inlineStr"/>
-      <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr"/>
-      <c r="AJ123" t="inlineStr"/>
-      <c r="AK123" t="inlineStr"/>
-      <c r="AL123" t="inlineStr"/>
-      <c r="AM123" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>HK$1,860,000,</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
         <is>
           <t>22:50</t>
         </is>
@@ -20606,7 +21165,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -20684,10 +21247,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1160</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -20777,7 +21342,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -20855,10 +21424,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1208</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -20948,7 +21519,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21026,10 +21601,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1148</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -21119,7 +21696,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21197,10 +21778,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1097</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -21290,7 +21873,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21368,10 +21955,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1155</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -21461,7 +22050,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21539,10 +22132,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -21632,7 +22227,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21710,10 +22309,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1081</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -21803,7 +22404,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -21881,10 +22486,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1087</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -21974,7 +22581,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22052,10 +22663,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1215</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -22145,7 +22758,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22227,10 +22844,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1105</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -22320,7 +22939,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22398,10 +23021,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1183</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -22491,7 +23116,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22569,10 +23198,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>965</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -22658,7 +23289,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22710,7 +23345,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1185</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -22769,7 +23406,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>80-60</t>
@@ -22821,7 +23462,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1157</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -23101,7 +23744,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -23126,7 +23773,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -23179,10 +23826,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1170</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -23272,7 +23921,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -23297,7 +23950,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -23350,10 +24003,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -23443,7 +24098,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -23521,10 +24180,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1193</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -23614,7 +24275,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -23625,7 +24290,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CONSPIRATOR</t>
+          <t>CONSPIRATOR (Scratched)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -23638,29 +24303,27 @@
           <t>K090</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>5</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>L Hewitson</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B Crawford</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>132</v>
-      </c>
-      <c r="T5" t="n">
-        <v>36</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -23668,24 +24331,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="W5" t="n">
-        <v>5</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9/10/12/13/8/5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>+ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -23696,7 +24361,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.57.67</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -23706,30 +24371,28 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>175,500</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>49</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Ng Sun Wah, Au Yau Lin &amp; Alan Leung Wai Zen</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Daiwa Major</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Get Closer</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AM5" t="b">
@@ -23781,7 +24444,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -23806,7 +24473,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -23859,10 +24526,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1186</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -23948,7 +24617,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -23973,7 +24646,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -24026,10 +24699,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1075</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -24115,7 +24790,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -24193,10 +24872,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1114</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -24282,7 +24963,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -24360,10 +25045,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1070</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -24453,7 +25140,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -24478,7 +25169,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -24531,10 +25222,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -24620,7 +25313,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -24645,7 +25342,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -24698,10 +25395,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -24791,7 +25490,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -24816,7 +25519,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -24869,10 +25572,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1260</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -24962,7 +25667,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -25040,10 +25749,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1173</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -25133,7 +25844,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -25185,7 +25900,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -25244,7 +25961,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>40-0</t>
@@ -25296,7 +26017,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1090</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -25576,7 +26299,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -25654,10 +26381,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1139</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -25747,7 +26476,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -25821,10 +26554,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1207</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -25914,7 +26649,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -25988,10 +26727,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1064</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -26077,7 +26818,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -26151,10 +26896,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>974</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -26244,7 +26991,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -26322,10 +27073,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1071</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -26415,7 +27168,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -26493,10 +27250,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1167</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -26586,7 +27345,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -26660,10 +27423,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1094</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -26749,7 +27514,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -26827,10 +27596,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1120</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -26916,7 +27687,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -26994,10 +27769,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1096</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -27087,7 +27864,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -27165,10 +27946,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1103</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -27258,7 +28041,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -27336,10 +28123,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1197</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -27429,7 +28218,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -27511,10 +28304,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1027</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -27604,7 +28399,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -27656,7 +28455,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1086</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -27715,7 +28516,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -27767,7 +28572,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1150</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -28047,7 +28854,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -28125,10 +28936,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -28218,7 +29031,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -28296,10 +29113,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>990</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -28389,7 +29208,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -28467,10 +29290,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1145</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -28560,7 +29385,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -28638,10 +29467,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1194</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -28731,7 +29562,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -28809,10 +29644,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1079</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -28902,7 +29739,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -28980,10 +29821,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1021</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
@@ -29069,7 +29912,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -29143,10 +29990,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1035</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -29236,7 +30085,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -29314,10 +30167,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1116</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -29407,7 +30262,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -29485,10 +30344,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1046</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+40</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -29578,7 +30439,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -29656,10 +30521,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1073</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -29749,7 +30616,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -29827,10 +30698,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1187</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -29920,7 +30793,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -29998,10 +30875,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1202</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -30091,7 +30970,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -30143,7 +31026,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1053</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -30202,7 +31087,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -30254,7 +31143,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1195</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -30534,7 +31425,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -30612,10 +31507,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1107</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -30705,7 +31602,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -30783,10 +31684,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1138</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -30876,7 +31779,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -30954,10 +31861,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1051</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -31047,7 +31956,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -31125,10 +32038,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1133</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -31218,7 +32133,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -31292,10 +32211,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1073</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -31381,7 +32302,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -31455,10 +32380,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1069</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+22</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -31548,7 +32475,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -31626,10 +32557,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1060</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -31719,7 +32652,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -31797,10 +32734,12 @@
           <t>+ * 1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1109</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -31890,7 +32829,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -31942,7 +32885,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1010</v>
+      </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -32001,7 +32946,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -32053,7 +33002,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1051</v>
+      </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -32333,7 +33284,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -32411,10 +33366,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1180</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -32500,7 +33457,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -32578,10 +33539,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1143</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -32671,7 +33634,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -32749,10 +33716,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1022</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -32842,7 +33811,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -32920,10 +33893,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1113</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -33013,7 +33988,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -33091,7 +34070,9 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1087</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
           <t>-</t>
@@ -33178,7 +34159,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -33256,10 +34241,12 @@
           <t>* 2</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -33349,7 +34336,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -33427,10 +34418,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1099</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -33520,7 +34513,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -33598,10 +34595,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1049</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -33687,7 +34686,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -33765,10 +34768,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1048</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -33858,7 +34863,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -33936,10 +34945,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1106</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -34029,7 +35040,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -34103,10 +35118,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1076</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -34196,7 +35213,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -34274,10 +35295,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1126</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -34367,7 +35390,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -34419,7 +35446,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1052</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -34478,7 +35507,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -34530,7 +35563,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1147</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -34810,7 +35845,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -34888,10 +35927,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1286</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -34981,7 +36022,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -35059,10 +36104,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1133</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -35152,7 +36199,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -35230,10 +36281,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1046</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -35323,7 +36376,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -35401,10 +36458,12 @@
           <t>+ 2</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1033</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -35494,7 +36553,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -35572,10 +36635,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1046</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -35665,7 +36730,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -35743,10 +36812,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1056</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -35836,7 +36907,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -35914,10 +36989,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1122</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -36007,7 +37084,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -36085,10 +37166,12 @@
           <t>+ 2</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1061</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -36178,7 +37261,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -36252,10 +37339,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1083</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -36345,7 +37434,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -36423,10 +37516,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1015</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -36516,7 +37611,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -36594,10 +37693,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -36687,7 +37788,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -36765,10 +37870,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1137</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -36858,7 +37965,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -36910,7 +38021,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1118</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -36969,7 +38082,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>60-40</t>
@@ -37021,7 +38138,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>996</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -37383,10 +38502,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1139</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -37558,10 +38679,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1031</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -37733,10 +38856,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1302</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -37908,10 +39033,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1131</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-35</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -38083,10 +39210,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1047</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -38254,7 +39383,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>1081</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>-</t>
@@ -38423,10 +39554,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1216</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -38598,10 +39731,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1078</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
@@ -38769,10 +39904,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1058</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -38944,10 +40081,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1144</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -39115,10 +40254,12 @@
           <t>* 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1130</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -39294,10 +40435,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1137</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -39443,7 +40586,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1220</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -39558,7 +40703,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>1070</v>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -39593,7 +40740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO15"/>
+  <dimension ref="A1:AO14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39838,7 +40985,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -39916,10 +41067,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>1211</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -40009,7 +41162,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -40083,10 +41240,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>1232</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -40176,7 +41335,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -40254,10 +41417,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1143</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -40347,7 +41512,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -40425,10 +41594,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>1081</v>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -40514,7 +41685,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -40592,10 +41767,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>1030</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -40685,7 +41862,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -40696,17 +41877,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>WITHOUT COMPARE</t>
+          <t>ROMANTIC THOR</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>HK_2025_L151</t>
+          <t>HK_2024_K012</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>L151</t>
+          <t>K012</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -40724,14 +41905,14 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -40740,7 +41921,7 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -40750,26 +41931,32 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1/2/1/4/2/4</t>
+          <t>3/4/1/4/2/3</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>XB/TT</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>1071</v>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr"/>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>1.48.49</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
           <t>-</t>
@@ -40777,25 +41964,25 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5,242,300</t>
+          <t>6,027,250</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Elaine Wong</t>
+          <t>Peter Lau Pak Fai &amp; Suki Tang Xianfang</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Brutal</t>
+          <t>Justify</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Command More</t>
+          <t>Wedding Vow</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -40852,7 +42039,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -40926,10 +42117,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1082</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -41019,7 +42212,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -41097,10 +42294,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>1140</v>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -41190,7 +42389,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -41268,10 +42471,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1039</v>
+      </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -41361,7 +42566,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -41439,10 +42648,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>1018</v>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -41532,7 +42743,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -41610,10 +42825,12 @@
           <t>+ 1</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>1151</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -41699,7 +42916,11 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>90-65</t>
@@ -41777,10 +42998,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1146</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -41870,18 +43093,22 @@
           <t>B</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yielding</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>90-65</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ROMANTIC THOR</t>
+          <t>SKY VINO</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -41891,30 +43118,30 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>C Fownes</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="T14" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3/4/1/4/2/3</t>
+          <t>4/6/1/2/6/7</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>XB/TT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -41922,7 +43149,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1100</v>
+      </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -41946,117 +43175,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HV</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HAT TRICK HANDICAP</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Turf</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>90-65</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SKY VINO</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>C Fownes</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>127</v>
-      </c>
-      <c r="T15" t="n">
-        <v>80</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="n">
-        <v>4</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>4/6/1/2/6/7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>HK$3,120,000,</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>22:15</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/racecards/racecard_20260708.xlsx
+++ b/racecards/racecard_20260708.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -18765,7 +18765,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -20181,7 +20181,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -20362,7 +20362,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -20712,7 +20712,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -22406,7 +22406,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -22583,7 +22583,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -24619,7 +24619,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -24792,7 +24792,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -24965,7 +24965,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -25142,7 +25142,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -25846,7 +25846,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -25963,7 +25963,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -26301,7 +26301,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -26993,7 +26993,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -27516,7 +27516,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -28220,7 +28220,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -28401,7 +28401,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -28518,7 +28518,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -28856,7 +28856,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -29210,7 +29210,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -29564,7 +29564,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -30087,7 +30087,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -30441,7 +30441,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -30618,7 +30618,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -31089,7 +31089,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -31427,7 +31427,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -31958,7 +31958,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -32135,7 +32135,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -32304,7 +32304,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -32477,7 +32477,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -32654,7 +32654,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -32831,7 +32831,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -33286,7 +33286,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -33459,7 +33459,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -34161,7 +34161,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -34338,7 +34338,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -34688,7 +34688,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -34865,7 +34865,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -35042,7 +35042,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -35215,7 +35215,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -35392,7 +35392,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -35509,7 +35509,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -36024,7 +36024,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -36201,7 +36201,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -36378,7 +36378,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -36732,7 +36732,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -36909,7 +36909,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -37086,7 +37086,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -37263,7 +37263,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -37613,7 +37613,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -37790,7 +37790,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -37967,7 +37967,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -38084,7 +38084,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -40987,7 +40987,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -41164,7 +41164,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -41337,7 +41337,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -41514,7 +41514,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -41687,7 +41687,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -41864,7 +41864,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -42041,7 +42041,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -42214,7 +42214,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -42391,7 +42391,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -42568,7 +42568,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -42745,7 +42745,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -43095,7 +43095,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yielding</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
